--- a/User_Stories.xlsx
+++ b/User_Stories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/22d7e69cf568a3bc/Documents/PythonProject/Final Project/FinalProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B1C85A1-DAC6-472A-A9CC-40A5A1144AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1DD50E3-3EF7-49CE-9C78-0BA97EF752D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="11448" windowHeight="9408" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="948" yWindow="1824" windowWidth="11448" windowHeight="7860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="58">
   <si>
     <t>ITSC-3155 Software Engineering</t>
   </si>
@@ -179,6 +179,18 @@
   </si>
   <si>
     <t>As a staff member, I want to access training materials so that I can use the system efficiently.</t>
+  </si>
+  <si>
+    <t>Restaurant Staff Management</t>
+  </si>
+  <si>
+    <t>Manage staff accounts and roles</t>
+  </si>
+  <si>
+    <t>Maintain efficient operations</t>
+  </si>
+  <si>
+    <t>As a staff member, I want to manage staff accounts so that I can maintain efficient operations</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -640,6 +652,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
@@ -910,7 +923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" ht="13.2">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -936,19 +949,33 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
+    <row r="13" spans="1:8" ht="13.2">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="H13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="13.2">
       <c r="A14" s="4"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -960,7 +987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="13.2">
       <c r="A15" s="4"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -972,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="13.2">
       <c r="A16" s="4"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -998,7 +1025,7 @@
     </row>
     <row r="18" spans="1:8" ht="15.6">
       <c r="A18" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -1007,7 +1034,7 @@
       <c r="F18" s="15"/>
       <c r="G18" s="16"/>
       <c r="H18" s="8">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1016,6 +1043,8 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A18:G18"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>